--- a/existing_customer/files/b2b_agentic_streamlit_demo_data.xlsx
+++ b/existing_customer/files/b2b_agentic_streamlit_demo_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sumandeep.a.kaur\Documents\B2B Agentic Screens Demo - Existing Customers\05_Feb\02-06_evening\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sumandeep.a.kaur\Documents\B2B Agentic Screens Demo - Existing Customers\b2b_leadmanagement_apps\existing_customer\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E265A7E5-64B6-4C90-8E1A-D9CBFDE2B694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D386A898-CEFF-4DD8-831C-775C02AE073C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="701" xr2:uid="{F9668476-116F-4EE7-B02C-E81D09556175}"/>
   </bookViews>
@@ -152,9 +152,6 @@
     <t>Account_Onboarding_Date</t>
   </si>
   <si>
-    <t>Active_Telstra_Products</t>
-  </si>
-  <si>
     <t>Internet_Primary_Contract_Start_Date</t>
   </si>
   <si>
@@ -440,9 +437,6 @@
     <t>• Business Expansion: Secured multiple multi-year civil infrastructure projects across NSW and QLD during FY24–FY25, increasing active construction sites.• Partnerships: Formed regional delivery partnerships to accelerate large-scale project execution.• Financials: Reported ~12% YoY revenue growth driven by sustained public infrastructure investment.</t>
   </si>
   <si>
-    <t>https://www.australianconstructionnews.com.au/ironbuild-secures-major-nsw-infrastructure-projects, https://www.infrainsights.com.au/ironbuild-expands-partner-network</t>
-  </si>
-  <si>
     <t>Company_Annual_SW_Spending_Bucket</t>
   </si>
   <si>
@@ -507,6 +501,12 @@
   </si>
   <si>
     <t>IronBuild Infrastructure</t>
+  </si>
+  <si>
+    <t>Active_Products</t>
+  </si>
+  <si>
+    <t>https://www.australianconstructionnews.com.au/ironbuild-secures-major-nsw-infrastructure-projects, https://www.infrainsights.com.au/ironbuild-expands-partner-network, https://www.afr.com.au/ironbuild-reports-strong-fy24-revenue-growth</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1025,7 @@
         <v>7</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>8</v>
@@ -1034,13 +1034,13 @@
         <v>24</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>6</v>
@@ -1061,226 +1061,226 @@
         <v>36</v>
       </c>
       <c r="T1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="U1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="U1" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="V1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="W1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ1" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="Y1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AK1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AJ1" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="AL1" s="4" t="s">
+      <c r="AM1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AM1" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="AN1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AO1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="AO1" s="4" t="s">
+      <c r="AP1" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="AQ1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AP1" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="AQ1" s="4" t="s">
+      <c r="AR1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AR1" s="4" t="s">
+      <c r="AS1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AS1" s="4" t="s">
+      <c r="AT1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="AT1" s="4" t="s">
+      <c r="AU1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="AU1" s="4" t="s">
+      <c r="AV1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AV1" s="4" t="s">
+      <c r="AW1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AW1" s="4" t="s">
+      <c r="AX1" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AX1" s="4" t="s">
+      <c r="AY1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="AY1" s="4" t="s">
+      <c r="AZ1" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="AZ1" s="4" t="s">
+      <c r="BA1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="BA1" s="4" t="s">
+      <c r="BB1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="BB1" s="4" t="s">
+      <c r="BC1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="BC1" s="4" t="s">
+      <c r="BD1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="BD1" s="4" t="s">
+      <c r="BE1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="BE1" s="4" t="s">
+      <c r="BF1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="BF1" s="4" t="s">
+      <c r="BG1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="BG1" s="4" t="s">
+      <c r="BH1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="BH1" s="4" t="s">
+      <c r="BI1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="BI1" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="BJ1" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="BK1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="BK1" s="4" t="s">
+      <c r="BL1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="BL1" s="4" t="s">
+      <c r="BM1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="BM1" s="4" t="s">
+      <c r="BN1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="BN1" s="4" t="s">
+      <c r="BO1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="BP1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="BO1" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="BP1" s="4" t="s">
+      <c r="BQ1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="BQ1" s="4" t="s">
+      <c r="BR1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="BR1" s="4" t="s">
+      <c r="BS1" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="BT1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="BU1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="BS1" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="BT1" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="BU1" s="4" t="s">
+      <c r="BV1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="BV1" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="BW1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BX1" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="BY1" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="BZ1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="BX1" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="BY1" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="BZ1" s="4" t="s">
+      <c r="CA1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="CA1" s="4" t="s">
+      <c r="CB1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="CB1" s="4" t="s">
+      <c r="CC1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="CC1" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="CD1" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="CE1" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="CE1" s="4" t="s">
+      <c r="CF1" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="CF1" s="4" t="s">
+      <c r="CG1" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="CG1" s="4" t="s">
+      <c r="CH1" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="CH1" s="4" t="s">
+      <c r="CI1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="CI1" s="4" t="s">
+      <c r="CJ1" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="CJ1" s="4" t="s">
+      <c r="CK1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="CK1" s="4" t="s">
+      <c r="CL1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="CL1" s="4" t="s">
+      <c r="CM1" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="CM1" s="4" t="s">
+      <c r="CN1" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="CN1" s="4" t="s">
+      <c r="CO1" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="CO1" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="CP1" s="4" t="s">
         <v>9</v>
@@ -1301,31 +1301,31 @@
         <v>32</v>
       </c>
       <c r="CV1" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="CW1" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="CW1" s="4" t="s">
+      <c r="CX1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="CX1" s="4" t="s">
+      <c r="CY1" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="CY1" s="4" t="s">
+      <c r="CZ1" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="CZ1" s="4" t="s">
+      <c r="DA1" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="DA1" s="4" t="s">
+      <c r="DB1" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="DB1" s="4" t="s">
+      <c r="DC1" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="DC1" s="4" t="s">
+      <c r="DD1" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="DD1" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="DE1" s="4" t="s">
         <v>11</v>
@@ -1339,13 +1339,13 @@
         <v>18</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E2" s="6">
         <v>2008</v>
@@ -1379,13 +1379,13 @@
         <v>26</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="S2" s="9">
-        <v>44348</v>
+        <v>44531</v>
       </c>
       <c r="T2" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U2" s="9">
         <v>42522</v>
@@ -1407,7 +1407,7 @@
         <v>0.85</v>
       </c>
       <c r="AA2" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AB2" s="10"/>
       <c r="AC2" s="10"/>
@@ -1431,7 +1431,7 @@
         <v>6</v>
       </c>
       <c r="AL2" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AM2" s="9">
         <v>43252</v>
@@ -1450,7 +1450,7 @@
         <v>180</v>
       </c>
       <c r="AR2" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AS2" s="10"/>
       <c r="AT2" s="10"/>
@@ -1472,16 +1472,16 @@
       <c r="BJ2" s="10"/>
       <c r="BK2" s="10"/>
       <c r="BL2" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="BM2" s="10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="BN2" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="BO2" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="BP2" s="11">
         <v>0.61</v>
@@ -1502,64 +1502,64 @@
         <v>1</v>
       </c>
       <c r="BV2" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BW2" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="BX2" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="BY2" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="BX2" s="10" t="s">
+      <c r="BZ2" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="BY2" s="10" t="s">
+      <c r="CA2" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="BZ2" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="CA2" s="10" t="s">
-        <v>140</v>
-      </c>
       <c r="CB2" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="CC2" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="CC2" s="10" t="s">
-        <v>98</v>
-      </c>
       <c r="CD2" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="CE2" s="10">
         <v>85</v>
       </c>
       <c r="CF2" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="CG2" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="CG2" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="CH2" s="10">
         <v>72</v>
       </c>
       <c r="CI2" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="CJ2" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="CJ2" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="CK2" s="10">
         <v>68</v>
       </c>
       <c r="CL2" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="CM2" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="CM2" s="10" t="s">
+      <c r="CN2" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="CO2" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="CN2" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="CO2" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="CP2" s="6" t="s">
         <v>27</v>
@@ -1580,37 +1580,37 @@
         <v>35</v>
       </c>
       <c r="CV2" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="CW2" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="CW2" s="14" t="s">
+      <c r="CX2" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="CX2" s="14" t="s">
+      <c r="CY2" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="CY2" s="14" t="s">
-        <v>131</v>
-      </c>
       <c r="CZ2" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="DA2" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="DB2" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="DA2" s="14" t="s">
+      <c r="DC2" s="14" t="s">
         <v>130</v>
-      </c>
-      <c r="DB2" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="DC2" s="14" t="s">
-        <v>131</v>
       </c>
       <c r="DD2" s="14" t="s">
         <v>2</v>
       </c>
       <c r="DE2" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="DF2" s="15" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
